--- a/02_加值成品/生物/生物6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物6-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物6-1 孟德爾的遺傳法則　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物6-1 孟德爾的遺傳法則　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>遺傳學之父是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>孟德爾</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>父與母</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>顯性</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>豌豆</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>孟德爾用什麼做實驗？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>豌豆</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>顯性遮蓋隱性</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>全Aa顯性</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>小寫字母</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>雜交</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>會表現出來的性狀是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>顯性</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>雜合(帶因)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>大寫字母</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>豌豆</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>表現</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>被遮蓋的性狀是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>隱性</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>父與母</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>成對</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>孟德爾</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>遮蓋</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>基因成對還單獨存在？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>顯性遮蓋隱性</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>成對</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>小寫字母</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>隱性</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>兩個</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>生殖細胞形成時基因會？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>分開</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>都顯性</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>隱性</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>顯性</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>分離律</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>顯性基因常用什麼表示？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>顯性</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>子代性狀比例</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>孟德爾</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>大寫字母</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>隱性基因常用什麼表示？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>小寫字母</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>顯性遮蓋隱性</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>孟德爾</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>子代性狀比例</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>控制生物性狀的遺傳因子稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>顯性遮蓋隱性</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>基因</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>孟德爾</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>父與母</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>一對基因分別來自？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>成對</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>顯性遮蓋隱性</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>父與母</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>小寫字母</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>雙親</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物6-1 孟德爾的遺傳法則　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物6-1 孟德爾的遺傳法則　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>Aa表現顯性還隱性？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>小寫字母</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>子代性狀比例</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>父與母</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>顯性</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>有A</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>aa表現顯性還隱性？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>隱性</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>分開</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>子代性狀比例</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>成對</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>無顯性</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>Aa×Aa子代顯隱性比約？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>成對</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>豌豆</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>大寫字母</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>孟德爾比</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>分離律指成對基因？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>隱性基因被攜帶未表現後代aa才顯現</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>分開進生殖細胞</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>AA與Aa皆表現顯性</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>父母皆為Aa帶隱性基因</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>分離</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>AA與Aa外表(性狀)？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>基因</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>大寫字母</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>豌豆</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>都顯性</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>相同</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>隱性性狀出現需基因型？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>顯性</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>都顯性</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>父與母</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>aa</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>兩隱性</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>生殖細胞各帶幾個某基因？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>一個</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>隱性</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>雜合(帶因)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>半數</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>遺傳圖解可推算什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>隱性</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>分開</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>子代性狀比例</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>豌豆</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>比例</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>純種顯性的基因型寫作？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>隱性</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>全Aa顯性</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>父與母</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>基因型</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>Aa這種基因型稱為？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>雜合(帶因)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>隱性</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>顯性</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>子代性狀比例</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>雜合</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物6-1 孟德爾的遺傳法則　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物6-1 孟德爾的遺傳法則　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>Aa×Aa子代基因型與比例？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>指是否表現非好壞</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>AA:Aa:aa=1:2:1</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>成對基因分開各生殖細胞帶一個</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>建立遺傳基本規律</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>推算</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何隱性性狀可能隔代出現？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>分開進生殖細胞</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>AA:Aa:aa=1:2:1</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>指是否表現非好壞</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>隱性基因被攜帶未表現後代aa才顯現</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>隔代</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>用分離律解釋生殖細胞基因分配？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>建立遺傳基本規律</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>父母皆為Aa帶隱性基因</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>成對基因分開各生殖細胞帶一個</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>3:1推親代皆Aa</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>分離</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>父母皆顯性卻生出隱性子代說明？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>父母皆為Aa帶隱性基因</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>AA:Aa:aa=1:2:1</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>指是否表現非好壞</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>建立遺傳基本規律</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>攜帶</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>AA×aa子代基因型與性狀？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>全Aa顯性</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>雜合(帶因)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>隱性</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>豌豆</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>雜交</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>顯性與隱性的正確理解？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>指是否表現非好壞</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>成對基因分開各生殖細胞帶一個</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>隱性基因被攜帶未表現後代aa才顯現</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>建立遺傳基本規律</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>觀念</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>如何由子代比例反推親代基因型？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>3:1推親代皆Aa</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>隱性基因被攜帶未表現後代aa才顯現</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>建立遺傳基本規律</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>成對基因分開各生殖細胞帶一個</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>反推</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>孟德爾實驗對遺傳學的意義？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>3:1推親代皆Aa</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>成對基因分開各生殖細胞帶一個</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>建立遺傳基本規律</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>指是否表現非好壞</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>意義</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>AA×Aa子代基因型與性狀？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>成對基因分開各生殖細胞帶一個</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>AA:Aa:aa=1:2:1</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>分開進生殖細胞</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>AA與Aa皆表現顯性</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>雜交</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何帶因者外表看不出攜帶隱性基因？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>孟德爾</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>成對</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>顯性遮蓋隱性</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>全Aa顯性</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>遮蓋</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物6-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>豌豆</t>
+          <t>遺傳學之父：孟德爾用豌豆做雜交實驗，發現了遺傳的基本規律，被稱為遺傳學之父</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>雜交</t>
+          <t>豌豆實驗：孟德爾選用性狀分明又容易栽培的豌豆，進行大量雜交實驗找出遺傳規律</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>表現</t>
+          <t>顯性表現：兩個不同基因同時存在時，會表現出來讓人看得到的性狀稱為顯性</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>遮蓋</t>
+          <t>隱性遮蓋：和顯性基因同時存在時會被遮蓋、不會表現出來的性狀稱為隱性</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>兩個</t>
+          <t>成對存在：控制性狀的基因在體細胞中是成對存在的，一個來自父方一個來自母方</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>分離律</t>
+          <t>基因分開：形成生殖細胞時，成對的基因會分開，各自進入不同的生殖細胞</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>符號表示：習慣上用大寫字母(如A)來代表顯性基因，方便寫出遺傳圖解</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>符號表示：習慣上用小寫字母(如a)來代表隱性基因，方便寫出遺傳圖解</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>單位：基因是控制生物遺傳性狀的基本單位，會由親代傳遞給子代</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>雙親</t>
+          <t>雙親：生物體內控制同一性狀的一對基因，一個來自父親、一個來自母親</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>有A</t>
+          <t>顯性表現：只要基因型中含有一個顯性基因A，個體外觀就會表現出顯性性狀</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>無顯性</t>
+          <t>隱性表現：基因型兩個都是隱性a，沒有顯性基因可以遮蓋，才會表現出隱性性狀</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>孟德爾比</t>
+          <t>孟德爾比例：Aa和Aa交配後，子代表現型顯性與隱性的比例大約是3比1</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>分離</t>
+          <t>分離律：成對的基因在形成生殖細胞時會彼此分開，各自進入不同的生殖細胞中</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>相同</t>
+          <t>外表相同：AA和Aa雖然基因型不同，但因為都含有顯性基因A，外表性狀都是顯性</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>兩隱性</t>
+          <t>需要兩個隱性：個體必須兩個基因都是隱性a，也就是基因型aa，隱性性狀才會表現出來</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>半數</t>
+          <t>各帶一個：成對基因在減數分裂時分開，所以每個生殖細胞只會帶到其中一個基因</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>比例</t>
+          <t>推算比例：畫出遺傳圖解可以幫助我們推算出子代各種基因型與性狀出現的比例</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>基因型</t>
+          <t>基因型：兩個都是顯性基因的組合寫成AA，代表純種顯性個體</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>雜合</t>
+          <t>雜合：一個顯性基因加一個隱性基因的組合稱為雜合子，外表雖表現顯性，但體內帶有隱性基因</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>推算</t>
+          <t>基因型比例：Aa與Aa交配後，子代基因型AA、Aa、aa出現的比例大約是1比2比1</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>隔代</t>
+          <t>隔代出現：父母雖表現顯性卻可能都帶有隱性基因(Aa)，子代若剛好得到兩個隱性基因aa，隱性性狀就會重新出現</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>分離</t>
+          <t>分離律解釋：體細胞中成對的基因在形成生殖細胞時會分開，讓每個生殖細胞只帶其中一個基因</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>攜帶</t>
+          <t>推知基因型：父母外表都是顯性卻生出隱性子代，代表雙方其實都是Aa，暗藏著一個隱性基因</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>雜交</t>
+          <t>固定結果：純種顯性AA與純種隱性aa交配，子代基因型必定全部是Aa，外表全部表現顯性</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>觀念</t>
+          <t>觀念釐清：顯性和隱性只是說明基因會不會表現出來，並不代表哪一種性狀比較優秀或比較差</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>反推</t>
+          <t>反推親代：若觀察到子代顯隱性比例接近3比1，就可以推測親代雙方基因型都是Aa</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>意義</t>
+          <t>奠定基礎：孟德爾透過豌豆實驗歸納出的分離律等規律，奠定了現代遺傳學的重要基礎</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>雜交</t>
+          <t>雜交：AA只能提供顯性基因A，Aa能提供A或a，配對後子代基因型是AA或Aa，因為都至少有一個顯性A，所以全部都表現顯性性狀</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>遮蓋</t>
+          <t>遮蓋：帶因者(Aa)體內雖然有一個隱性基因a，但顯性基因A的表現會遮蓋住隱性基因，所以外表仍表現顯性性狀，看不出來帶有隱性基因</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物6-1_三種難度測驗卷.xlsx
@@ -648,17 +648,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>雜合(帶因)</t>
+          <t>成對</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>大寫字母</t>
+          <t>分開</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>豌豆</t>
+          <t>孟德爾</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>父與母</t>
+          <t>顯性</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>全Aa顯性</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>小寫字母</t>
+          <t>成對</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>子代性狀比例</t>
+          <t>豌豆</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>父與母</t>
+          <t>大寫字母</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>分開</t>
+          <t>孟德爾</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>子代性狀比例</t>
+          <t>顯性</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1119,22 +1119,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>父與母</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>都顯性</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>豌豆</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>大寫字母</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>豌豆</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>孟德爾</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>基因</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>大寫字母</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>豌豆</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1680,17 +1680,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>雜合(帶因)</t>
+          <t>隱性</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>隱性</t>
+          <t>小寫字母</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>豌豆</t>
+          <t>分開</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>孟德爾</t>
+          <t>成對</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>全Aa顯性</t>
+          <t>大寫字母</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
